--- a/IJKL作業.xlsx
+++ b/IJKL作業.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC05718C-956A-462F-881F-BDA074D7336D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E125FBFE-D7E5-4502-B2C6-3E046D39B0A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="対応状況一覧" sheetId="1" r:id="rId1"/>
-    <sheet name="参照データ" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="参照データ" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1486,8 +1486,9 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/IJKL作業.xlsx
+++ b/IJKL作業.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E125FBFE-D7E5-4502-B2C6-3E046D39B0A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE3B75B-98AF-4E14-B5E6-3D60BD047161}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="対応状況一覧" sheetId="1" r:id="rId1"/>

--- a/IJKL作業.xlsx
+++ b/IJKL作業.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE3B75B-98AF-4E14-B5E6-3D60BD047161}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCE6036-B134-40FE-8DEC-A7E27DACAD8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="対応状況一覧" sheetId="1" r:id="rId1"/>
-    <sheet name="参照データ" sheetId="2" r:id="rId2"/>
+    <sheet name="参照データ" sheetId="2" r:id="rId1"/>
+    <sheet name="対応状況一覧" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -611,6 +611,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferenceDataTable" displayName="ReferenceDataTable" ref="A2:F14" totalsRowShown="0">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="顧客ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="氏名"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="生年月日"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="電話番号"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="住所"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="取扱区分"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="WorkStatusTable" displayName="WorkStatusTable" ref="A3:H15" totalsRowShown="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="管理番号"/>
@@ -621,20 +635,6 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ステータス"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="顧客ID"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="備考"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferenceDataTable" displayName="ReferenceDataTable" ref="A2:F14" totalsRowShown="0">
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="顧客ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="氏名"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="生年月日"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="電話番号"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="住所"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="取扱区分"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -834,6 +834,289 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:F14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" ht="15">
+      <c r="A2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="1">
+        <v>30056</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="1">
+        <v>29162</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="1">
+        <v>33046</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="1">
+        <v>31298</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="1">
+        <v>27442</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="1">
+        <v>34314</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="1">
+        <v>32353</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="1">
+        <v>34762</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="1">
+        <v>29513</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="1">
+        <v>31923</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="1">
+        <v>33463</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="23">
+        <v>30711</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1208,287 +1491,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:F14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="1">
-        <v>30056</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="1">
-        <v>29162</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="1">
-        <v>33046</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="1">
-        <v>31298</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="1">
-        <v>27442</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="1">
-        <v>34314</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="1">
-        <v>32353</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="1">
-        <v>34762</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="1">
-        <v>29513</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="1">
-        <v>31923</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="1">
-        <v>33463</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="23">
-        <v>30711</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>